--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_atacama.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_atacama.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>29.00008927774306</v>
+      </c>
+      <c r="C2">
         <v>24.69333095259352</v>
-      </c>
-      <c r="C2">
-        <v>29.00008927774306</v>
       </c>
       <c r="D2">
         <v>4.049676416356339</v>
       </c>
       <c r="E2">
-        <v>16.06661554904967</v>
+        <v>18.86879037129978</v>
       </c>
       <c r="F2">
         <v>65.06459407965053</v>
       </c>
       <c r="G2">
-        <v>18.86879037129978</v>
+        <v>16.06661554904967</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>30.36396227885589</v>
+      </c>
+      <c r="C3">
         <v>30.22367703218767</v>
-      </c>
-      <c r="C3">
-        <v>30.36396227885589</v>
       </c>
       <c r="D3">
         <v>3.308664259927798</v>
       </c>
       <c r="E3">
-        <v>18.82067459354526</v>
+        <v>18.90803203106042</v>
       </c>
       <c r="F3">
-        <v>62.27129337539433</v>
+        <v>62.27129337539432</v>
       </c>
       <c r="G3">
-        <v>18.90803203106042</v>
+        <v>18.82067459354525</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>32.49910618519843</v>
+      </c>
+      <c r="C4">
         <v>22.64330830651889</v>
-      </c>
-      <c r="C4">
-        <v>32.49910618519843</v>
       </c>
       <c r="D4">
         <v>4.416315789473685</v>
       </c>
       <c r="E4">
-        <v>14.59517591027808</v>
+        <v>20.9479182670149</v>
       </c>
       <c r="F4">
         <v>64.45690582270701</v>
       </c>
       <c r="G4">
-        <v>20.9479182670149</v>
+        <v>14.59517591027808</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>31.02603011555971</v>
+      </c>
+      <c r="C5">
         <v>32.39173573012723</v>
-      </c>
-      <c r="C5">
-        <v>31.02603011555971</v>
       </c>
       <c r="D5">
         <v>3.087207207207207</v>
       </c>
       <c r="E5">
-        <v>19.82142857142857</v>
+        <v>18.98571428571428</v>
       </c>
       <c r="F5">
         <v>61.19285714285714</v>
       </c>
       <c r="G5">
-        <v>18.98571428571428</v>
+        <v>19.82142857142857</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.41176470588236</v>
+      </c>
+      <c r="C6">
         <v>22.86938397406207</v>
-      </c>
-      <c r="C6">
-        <v>29.41176470588236</v>
       </c>
       <c r="D6">
         <v>4.372658227848102</v>
       </c>
       <c r="E6">
-        <v>15.0178693635465</v>
+        <v>19.31412059919398</v>
       </c>
       <c r="F6">
         <v>65.66801003725953</v>
       </c>
       <c r="G6">
-        <v>19.31412059919398</v>
+        <v>15.0178693635465</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>29.35414667193587</v>
+      </c>
+      <c r="C7">
         <v>32.09507141647377</v>
-      </c>
-      <c r="C7">
-        <v>29.35414667193587</v>
       </c>
       <c r="D7">
         <v>3.115743183817063</v>
       </c>
       <c r="E7">
+        <v>18.1816592359472</v>
+      </c>
+      <c r="F7">
+        <v>61.93898068012939</v>
+      </c>
+      <c r="G7">
         <v>19.87936008392342</v>
-      </c>
-      <c r="F7">
-        <v>61.93898068012938</v>
-      </c>
-      <c r="G7">
-        <v>18.1816592359472</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>29.99643747773423</v>
+      </c>
+      <c r="C8">
         <v>43.74777342358389</v>
-      </c>
-      <c r="C8">
-        <v>29.99643747773423</v>
       </c>
       <c r="D8">
         <v>2.285830618892508</v>
       </c>
       <c r="E8">
-        <v>25.17941357391839</v>
+        <v>17.26471191306131</v>
       </c>
       <c r="F8">
         <v>57.5558745130203</v>
       </c>
       <c r="G8">
-        <v>17.26471191306131</v>
+        <v>25.17941357391839</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>32.10208193418402</v>
+      </c>
+      <c r="C9">
         <v>33.31094694425789</v>
-      </c>
-      <c r="C9">
-        <v>32.10208193418402</v>
       </c>
       <c r="D9">
         <v>3.002016129032258</v>
       </c>
       <c r="E9">
-        <v>20.13804303694682</v>
+        <v>19.4072269589931</v>
       </c>
       <c r="F9">
         <v>60.45473000406009</v>
       </c>
       <c r="G9">
-        <v>19.4072269589931</v>
+        <v>20.13804303694682</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>31.16789374909774</v>
+      </c>
+      <c r="C10">
         <v>35.05124873682691</v>
-      </c>
-      <c r="C10">
-        <v>31.16789374909774</v>
       </c>
       <c r="D10">
         <v>2.852965403624382</v>
       </c>
       <c r="E10">
-        <v>21.08737189508424</v>
+        <v>18.75108563487928</v>
       </c>
       <c r="F10">
         <v>60.16154247003648</v>
       </c>
       <c r="G10">
-        <v>18.75108563487928</v>
+        <v>21.08737189508424</v>
       </c>
     </row>
   </sheetData>
